--- a/pyepidemics-master/data/shanghai/上海H3N2_SEIR代理数据集_2017.xlsx
+++ b/pyepidemics-master/data/shanghai/上海H3N2_SEIR代理数据集_2017.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/15ae6bb5f11cf73f/Desktop/学校/课程/专业课/数学建模/课程项目/pyepidemics-master/data/shanghai/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/15ae6bb5f11cf73f/Desktop/学校/课程/专业课/数学建模/课程项目/Mathematical-Modeling-Course-Project/pyepidemics-master/data/shanghai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{EE8D85E2-80C6-4BDF-BCBC-DBA62900AC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{613A4CF3-4ADA-4DA7-8D8A-87317117C68D}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{EE8D85E2-80C6-4BDF-BCBC-DBA62900AC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F0C5A8-4B4A-4A48-AF1B-6EDA311D7862}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概览" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="136">
   <si>
     <t>上海 H3N2 2017 SEIR 代理数据集</t>
   </si>
@@ -363,9 +363,6 @@
     <t>代理曲线锚点</t>
   </si>
   <si>
-    <t>https://ivdc.chinacdc.cn/cnic/zyzx/lgzb/201708/t20170807_149211.htm</t>
-  </si>
-  <si>
     <t>国家流感中心 2017 第33周</t>
   </si>
   <si>
@@ -437,6 +434,14 @@
   <si>
     <t>序列间隔与传染期简化</t>
   </si>
+  <si>
+    <t>https://ivdc.chinacdc.cn/cnic/zyzx/lgzb/201708/t20170807_149211.htm</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.who.int/news-room/fact-sheets/detail/influenza-%28seasonal%EF%BC%89</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -446,7 +451,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,6 +483,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -517,10 +530,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -540,9 +554,11 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -562,27 +578,16 @@
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
   <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="zh-CN" altLang="en-US"/>
-              <a:t>新感染数与新报告病例数</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
@@ -603,9 +608,13 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -1394,9 +1403,13 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -2185,9 +2198,13 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -2976,9 +2993,13 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
@@ -3760,6 +3781,21 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                  <a:alpha val="33000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
         <c:smooth val="0"/>
         <c:axId val="10"/>
         <c:axId val="100"/>
@@ -3774,20 +3810,57 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US"/>
+                  <a:rPr lang="zh-CN"/>
                   <a:t>日期</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:overlay val="1"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="yyyy\-mm\-dd" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -3804,44 +3877,178 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="zh-CN" altLang="en-US"/>
+                  <a:rPr lang="zh-CN"/>
                   <a:t>人数</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
           <c:overlay val="1"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="10"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="1"/>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -7145,6 +7352,584 @@
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="230">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="0" kern="1200" spc="20" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+            <a:alpha val="33000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="95000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" spc="20" baseline="0"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15651,10 +16436,10 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="47" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="72" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="109.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28" x14ac:dyDescent="0.25">
@@ -15695,8 +16480,8 @@
       <c r="C3" t="s">
         <v>109</v>
       </c>
-      <c r="D3" t="s">
-        <v>110</v>
+      <c r="D3" s="11" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -15704,13 +16489,13 @@
         <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
         <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -15718,13 +16503,13 @@
         <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
         <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -15732,24 +16517,24 @@
         <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
         <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" t="s">
         <v>117</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>118</v>
-      </c>
-      <c r="C7" t="s">
-        <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -15757,27 +16542,27 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
         <v>120</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>121</v>
-      </c>
-      <c r="D8" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" t="s">
         <v>123</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>124</v>
-      </c>
-      <c r="C9" t="s">
-        <v>125</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -15785,24 +16570,24 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" t="s">
         <v>126</v>
       </c>
-      <c r="C10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
+      <c r="D10" s="11" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" t="s">
         <v>128</v>
-      </c>
-      <c r="B11" t="s">
-        <v>129</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
@@ -15813,13 +16598,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" t="s">
         <v>130</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>131</v>
-      </c>
-      <c r="C12" t="s">
-        <v>132</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
@@ -15827,13 +16612,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
         <v>133</v>
-      </c>
-      <c r="C13" t="s">
-        <v>134</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -15842,6 +16627,10 @@
   </sheetData>
   <autoFilter ref="A1:D13" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{C2C2EE3B-D626-421F-9B8B-9C8AC1008293}"/>
+    <hyperlink ref="D10" r:id="rId2" xr:uid="{F33B66A5-7F02-4DFE-860C-B3CAD693E246}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
